--- a/data/trans_orig/Q4503_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q4503_R-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2007</t>
+          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2007 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67411</t>
+          <t>69652</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104134</t>
+          <t>101801</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21564</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41512</t>
+          <t>42348</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95638</t>
+          <t>96179</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136941</t>
+          <t>135281</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69659</t>
+          <t>68964</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104131</t>
+          <t>103964</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30561</t>
+          <t>29504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55382</t>
+          <t>53782</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107707</t>
+          <t>108383</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149820</t>
+          <t>150082</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>122099</t>
+          <t>121916</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164372</t>
+          <t>161709</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77684</t>
+          <t>78374</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>109949</t>
+          <t>111172</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>210176</t>
+          <t>212469</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>262011</t>
+          <t>265290</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43430</t>
+          <t>44992</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74303</t>
+          <t>72651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35058</t>
+          <t>35551</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61257</t>
+          <t>59717</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86778</t>
+          <t>85421</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125147</t>
+          <t>125896</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85025</t>
+          <t>87623</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>122680</t>
+          <t>121731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75786</t>
+          <t>75616</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107377</t>
+          <t>107972</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>172069</t>
+          <t>173113</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>220467</t>
+          <t>219727</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48598</t>
+          <t>50262</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77996</t>
+          <t>80037</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33944</t>
+          <t>35188</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60339</t>
+          <t>62051</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91388</t>
+          <t>93004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130797</t>
+          <t>132815</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43397</t>
+          <t>44436</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71177</t>
+          <t>72851</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31747</t>
+          <t>31566</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57813</t>
+          <t>56896</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81601</t>
+          <t>83126</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>119986</t>
+          <t>119767</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84154</t>
+          <t>81148</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117507</t>
+          <t>117607</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>81970</t>
+          <t>83262</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>116997</t>
+          <t>118637</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>176024</t>
+          <t>176788</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>226186</t>
+          <t>225726</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25934</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50401</t>
+          <t>51707</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39201</t>
+          <t>38748</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65582</t>
+          <t>64371</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70992</t>
+          <t>71225</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107492</t>
+          <t>107442</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90436</t>
+          <t>92166</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>126673</t>
+          <t>127166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113717</t>
+          <t>111664</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>150396</t>
+          <t>149935</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>211901</t>
+          <t>212436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>264208</t>
+          <t>265843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80021</t>
+          <t>77523</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>117550</t>
+          <t>116124</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29944</t>
+          <t>28515</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98037</t>
+          <t>99818</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>138235</t>
+          <t>139205</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89109</t>
+          <t>89059</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>124884</t>
+          <t>126526</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14294</t>
+          <t>14380</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32205</t>
+          <t>32219</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>106683</t>
+          <t>106369</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>148967</t>
+          <t>149901</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136480</t>
+          <t>135718</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>177391</t>
+          <t>178959</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31622</t>
+          <t>31393</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54559</t>
+          <t>55127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>179136</t>
+          <t>176022</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>227587</t>
+          <t>225777</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,79%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40141</t>
+          <t>39505</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67799</t>
+          <t>66440</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>11110</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29517</t>
+          <t>28320</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55526</t>
+          <t>56774</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88996</t>
+          <t>88304</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>109095</t>
+          <t>109661</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>148227</t>
+          <t>150175</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51769</t>
+          <t>50618</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76707</t>
+          <t>75612</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>168094</t>
+          <t>167849</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216476</t>
+          <t>214779</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>253573</t>
+          <t>250764</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>314400</t>
+          <t>309309</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65928</t>
+          <t>65420</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>99697</t>
+          <t>98545</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>327660</t>
+          <t>330044</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>396931</t>
+          <t>398177</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>219399</t>
+          <t>221076</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>272647</t>
+          <t>274597</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>68852</t>
+          <t>70053</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>104090</t>
+          <t>105288</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>300834</t>
+          <t>302687</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>366476</t>
+          <t>369067</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>309958</t>
+          <t>310327</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>373525</t>
+          <t>373489</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>157514</t>
+          <t>156823</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>203377</t>
+          <t>202390</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>481583</t>
+          <t>485473</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>558962</t>
+          <t>560496</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85562</t>
+          <t>87105</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>125264</t>
+          <t>123811</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76675</t>
+          <t>74976</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112444</t>
+          <t>112522</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>173147</t>
+          <t>173114</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>229795</t>
+          <t>226652</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>232721</t>
+          <t>232599</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>291228</t>
+          <t>289845</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>249199</t>
+          <t>247824</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>301845</t>
+          <t>297170</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>493798</t>
+          <t>490705</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>571671</t>
+          <t>571583</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>68067</t>
+          <t>64897</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>99341</t>
+          <t>96048</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>55967</t>
+          <t>54726</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>85957</t>
+          <t>86018</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>129503</t>
+          <t>127397</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>175042</t>
+          <t>173345</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>54819</t>
+          <t>52272</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>84193</t>
+          <t>83872</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>49853</t>
+          <t>48741</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>79591</t>
+          <t>78609</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>111822</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>154627</t>
+          <t>154899</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>89506</t>
+          <t>90711</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>125945</t>
+          <t>127595</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>116165</t>
+          <t>117754</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>157358</t>
+          <t>158914</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>216789</t>
+          <t>217988</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>273044</t>
+          <t>273391</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,74%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14811</t>
+          <t>14922</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32162</t>
+          <t>33766</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>67274</t>
+          <t>65814</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>100681</t>
+          <t>100615</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>86756</t>
+          <t>86991</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>126103</t>
+          <t>126074</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>57878</t>
+          <t>56056</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>87192</t>
+          <t>87030</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>194964</t>
+          <t>193417</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>242658</t>
+          <t>242101</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>257124</t>
+          <t>258430</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>315042</t>
+          <t>315453</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,31%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>16385</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>34429</t>
+          <t>34612</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>110250</t>
+          <t>113599</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>153636</t>
+          <t>154233</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>132664</t>
+          <t>134188</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>182005</t>
+          <t>184692</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>39464</t>
+          <t>39716</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>65246</t>
+          <t>66244</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>94418</t>
+          <t>93577</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>133083</t>
+          <t>136377</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>141893</t>
+          <t>142685</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>189540</t>
+          <t>190781</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>97539</t>
+          <t>96198</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>130576</t>
+          <t>130130</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>258029</t>
+          <t>259386</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>321577</t>
+          <t>321397</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>366969</t>
+          <t>370735</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>436753</t>
+          <t>438749</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>24455</t>
+          <t>25917</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>47986</t>
+          <t>46765</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>115885</t>
+          <t>114956</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>157585</t>
+          <t>158590</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>147723</t>
+          <t>148290</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>196129</t>
+          <t>195838</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>59353</t>
+          <t>59712</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>89577</t>
+          <t>90392</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>542046</t>
+          <t>539878</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>612534</t>
+          <t>610635</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>615633</t>
+          <t>609786</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>691193</t>
+          <t>690271</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,68%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>592073</t>
+          <t>590923</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>684127</t>
+          <t>679173</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>346891</t>
+          <t>342567</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>419926</t>
+          <t>417559</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>956775</t>
+          <t>951617</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1079926</t>
+          <t>1071079</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>573486</t>
+          <t>569751</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>669974</t>
+          <t>660895</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>338865</t>
+          <t>334555</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>411044</t>
+          <t>409442</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>926522</t>
+          <t>927946</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1043582</t>
+          <t>1042129</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>909372</t>
+          <t>912894</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1016806</t>
+          <t>1018376</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>787960</t>
+          <t>792018</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>891342</t>
+          <t>887007</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1739942</t>
+          <t>1732581</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1883919</t>
+          <t>1878806</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>277201</t>
+          <t>280760</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>344114</t>
+          <t>347230</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>389189</t>
+          <t>390013</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>469853</t>
+          <t>467670</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>688275</t>
+          <t>686131</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>786877</t>
+          <t>789593</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>689365</t>
+          <t>695117</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>791133</t>
+          <t>792436</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1296360</t>
+          <t>1298907</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1415327</t>
+          <t>1412449</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2026204</t>
+          <t>2024073</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2172904</t>
+          <t>2174632</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2012 (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80214</t>
+          <t>80822</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>116004</t>
+          <t>117380</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35302</t>
+          <t>35767</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64103</t>
+          <t>64590</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>124125</t>
+          <t>125255</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>170895</t>
+          <t>172709</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69668</t>
+          <t>67611</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105514</t>
+          <t>102036</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55540</t>
+          <t>55327</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86516</t>
+          <t>87113</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133545</t>
+          <t>131769</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>182312</t>
+          <t>177190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93972</t>
+          <t>92883</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131213</t>
+          <t>134020</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52868</t>
+          <t>53705</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83473</t>
+          <t>84597</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>158302</t>
+          <t>158790</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>206701</t>
+          <t>209620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17687</t>
+          <t>16447</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38763</t>
+          <t>38395</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22750</t>
+          <t>21879</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44975</t>
+          <t>45437</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43905</t>
+          <t>45609</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76033</t>
+          <t>78725</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97389</t>
+          <t>95043</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137357</t>
+          <t>136285</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74179</t>
+          <t>73816</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108690</t>
+          <t>108819</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>178792</t>
+          <t>177057</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>231546</t>
+          <t>231795</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,03%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79368</t>
+          <t>79797</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119045</t>
+          <t>116871</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38973</t>
+          <t>39616</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68634</t>
+          <t>69271</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130293</t>
+          <t>127864</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175739</t>
+          <t>174066</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65958</t>
+          <t>65792</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104227</t>
+          <t>102626</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38870</t>
+          <t>36856</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65592</t>
+          <t>64331</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113396</t>
+          <t>112865</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>157408</t>
+          <t>158586</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77558</t>
+          <t>76627</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116192</t>
+          <t>116033</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63130</t>
+          <t>62049</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>94323</t>
+          <t>95470</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>150793</t>
+          <t>149617</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>196428</t>
+          <t>200757</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14964</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35041</t>
+          <t>34615</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30780</t>
+          <t>29879</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57529</t>
+          <t>57073</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51120</t>
+          <t>51890</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84561</t>
+          <t>84440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97517</t>
+          <t>97969</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135560</t>
+          <t>136823</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96468</t>
+          <t>95275</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133681</t>
+          <t>134180</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>202562</t>
+          <t>203363</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>258015</t>
+          <t>256936</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>155085</t>
+          <t>154198</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>201217</t>
+          <t>200693</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47025</t>
+          <t>46377</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73762</t>
+          <t>72811</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>210882</t>
+          <t>209859</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>263626</t>
+          <t>263315</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94020</t>
+          <t>96550</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134778</t>
+          <t>135106</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21642</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45493</t>
+          <t>43706</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123539</t>
+          <t>125331</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>169036</t>
+          <t>171362</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>110758</t>
+          <t>111910</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>153991</t>
+          <t>151945</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40170</t>
+          <t>39803</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66833</t>
+          <t>66754</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>158344</t>
+          <t>156921</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>208683</t>
+          <t>207677</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16645</t>
+          <t>16580</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36809</t>
+          <t>36948</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>17041</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37158</t>
+          <t>36930</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37148</t>
+          <t>38232</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65618</t>
+          <t>67993</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>157857</t>
+          <t>155561</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>204768</t>
+          <t>203831</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75030</t>
+          <t>76253</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>105739</t>
+          <t>106367</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>243804</t>
+          <t>245816</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>296557</t>
+          <t>302029</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>269979</t>
+          <t>272304</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>331461</t>
+          <t>331053</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>110548</t>
+          <t>107707</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>152953</t>
+          <t>152396</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>391607</t>
+          <t>392011</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>466968</t>
+          <t>467219</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>201237</t>
+          <t>199875</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>260872</t>
+          <t>255674</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>95680</t>
+          <t>95623</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>138367</t>
+          <t>135696</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>308737</t>
+          <t>311627</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>377190</t>
+          <t>383464</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>168149</t>
+          <t>170943</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>221672</t>
+          <t>224225</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>131119</t>
+          <t>131564</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>176061</t>
+          <t>176644</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>317676</t>
+          <t>313427</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>383016</t>
+          <t>387649</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>43355</t>
+          <t>42896</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>73183</t>
+          <t>75577</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47239</t>
+          <t>47598</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77087</t>
+          <t>77237</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>95913</t>
+          <t>96086</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>140649</t>
+          <t>140658</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>343651</t>
+          <t>339930</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>410121</t>
+          <t>407457</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>281060</t>
+          <t>282630</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>338551</t>
+          <t>338391</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>636552</t>
+          <t>640518</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>725474</t>
+          <t>728378</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,9%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>115729</t>
+          <t>116356</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>156911</t>
+          <t>155829</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>88057</t>
+          <t>86924</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>127972</t>
+          <t>128880</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>217513</t>
+          <t>215947</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>276833</t>
+          <t>272344</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>77510</t>
+          <t>76576</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>114093</t>
+          <t>112088</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>88123</t>
+          <t>88829</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>128052</t>
+          <t>129050</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>177144</t>
+          <t>175582</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>228923</t>
+          <t>228300</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>70167</t>
+          <t>70603</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>106106</t>
+          <t>105685</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>98905</t>
+          <t>98300</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>139758</t>
+          <t>141234</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>181557</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>234757</t>
+          <t>233705</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14673</t>
+          <t>15106</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>33369</t>
+          <t>34569</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>48786</t>
+          <t>47125</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>78591</t>
+          <t>78824</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>70258</t>
+          <t>69730</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>103948</t>
+          <t>105079</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>149134</t>
+          <t>147929</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>192078</t>
+          <t>190737</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>334089</t>
+          <t>335024</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>388217</t>
+          <t>389191</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>492938</t>
+          <t>494945</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>564022</t>
+          <t>565248</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,59%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>33411</t>
+          <t>34016</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>58439</t>
+          <t>58913</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>129389</t>
+          <t>129518</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>174537</t>
+          <t>177629</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>171465</t>
+          <t>170072</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>224344</t>
+          <t>226259</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>42014</t>
+          <t>42606</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>66678</t>
+          <t>68499</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>122893</t>
+          <t>122160</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>169278</t>
+          <t>167977</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>171846</t>
+          <t>171543</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>223257</t>
+          <t>223008</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>52732</t>
+          <t>52456</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>79072</t>
+          <t>79449</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>189375</t>
+          <t>188202</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>241916</t>
+          <t>241589</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>249997</t>
+          <t>250660</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>309925</t>
+          <t>310297</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16533</t>
+          <t>16845</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>34733</t>
+          <t>35311</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>88475</t>
+          <t>86168</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>126905</t>
+          <t>124051</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>110797</t>
+          <t>109423</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>155479</t>
+          <t>154942</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>63387</t>
+          <t>63864</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>94602</t>
+          <t>91691</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>457269</t>
+          <t>457808</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>524637</t>
+          <t>524303</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>530616</t>
+          <t>533851</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>607864</t>
+          <t>608461</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,28%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>806065</t>
+          <t>803300</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>910614</t>
+          <t>906830</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>508249</t>
+          <t>503727</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>595596</t>
+          <t>595009</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1330039</t>
+          <t>1337384</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1475038</t>
+          <t>1472605</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>614805</t>
+          <t>613004</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>711515</t>
+          <t>711074</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>477531</t>
+          <t>477006</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>567092</t>
+          <t>564796</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1123873</t>
+          <t>1113924</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1255454</t>
+          <t>1247715</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>641072</t>
+          <t>642359</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>734935</t>
+          <t>742731</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>637889</t>
+          <t>637458</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>743204</t>
+          <t>735255</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1306808</t>
+          <t>1307941</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1443089</t>
+          <t>1444272</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>153298</t>
+          <t>155295</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>206175</t>
+          <t>207837</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>294174</t>
+          <t>293148</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>364841</t>
+          <t>365856</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>464644</t>
+          <t>464230</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>556346</t>
+          <t>553073</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>980243</t>
+          <t>975001</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1090147</t>
+          <t>1088509</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1393072</t>
+          <t>1395545</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1511863</t>
+          <t>1511930</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2401418</t>
+          <t>2399488</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2575111</t>
+          <t>2568157</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2016 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63101</t>
+          <t>63410</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95401</t>
+          <t>99043</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36390</t>
+          <t>36836</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62369</t>
+          <t>63095</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107486</t>
+          <t>105702</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>151054</t>
+          <t>150840</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106977</t>
+          <t>107646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146777</t>
+          <t>146797</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73767</t>
+          <t>74712</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>108067</t>
+          <t>109029</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>192035</t>
+          <t>191229</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242221</t>
+          <t>240042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,96%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80298</t>
+          <t>79646</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117635</t>
+          <t>117178</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>73900</t>
+          <t>76822</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>109237</t>
+          <t>108030</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>166980</t>
+          <t>165569</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>213875</t>
+          <t>213491</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20128</t>
+          <t>20509</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43379</t>
+          <t>44277</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30908</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55349</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56909</t>
+          <t>57262</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90871</t>
+          <t>92183</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77084</t>
+          <t>77914</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>111990</t>
+          <t>113095</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59133</t>
+          <t>60661</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91187</t>
+          <t>90988</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147001</t>
+          <t>147011</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>193125</t>
+          <t>192310</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42913</t>
+          <t>44182</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73936</t>
+          <t>74351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29825</t>
+          <t>29951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55125</t>
+          <t>56394</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80732</t>
+          <t>80411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118203</t>
+          <t>120958</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90890</t>
+          <t>90231</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127757</t>
+          <t>127413</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97470</t>
+          <t>95249</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132411</t>
+          <t>131776</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>197890</t>
+          <t>194874</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>247021</t>
+          <t>245520</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76464</t>
+          <t>76154</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109077</t>
+          <t>110072</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71505</t>
+          <t>70951</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>103609</t>
+          <t>105964</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>155496</t>
+          <t>156750</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>205435</t>
+          <t>203447</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13494</t>
+          <t>13413</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30408</t>
+          <t>30520</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>20240</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43316</t>
+          <t>41947</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37791</t>
+          <t>37621</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65193</t>
+          <t>64630</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79810</t>
+          <t>80682</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115986</t>
+          <t>113912</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80649</t>
+          <t>81142</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114759</t>
+          <t>116511</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171233</t>
+          <t>171268</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>219063</t>
+          <t>221366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74635</t>
+          <t>75559</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110253</t>
+          <t>109292</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14474</t>
+          <t>14080</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32720</t>
+          <t>33755</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94457</t>
+          <t>95912</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134202</t>
+          <t>136056</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115517</t>
+          <t>115992</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154455</t>
+          <t>154881</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24676</t>
+          <t>25062</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46038</t>
+          <t>46388</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>149832</t>
+          <t>147380</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>195265</t>
+          <t>193978</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>109821</t>
+          <t>111888</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>149888</t>
+          <t>150537</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22679</t>
+          <t>23260</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43697</t>
+          <t>43798</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>140857</t>
+          <t>141227</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>186871</t>
+          <t>186008</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31732</t>
+          <t>31006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58653</t>
+          <t>56475</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23175</t>
+          <t>22698</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44007</t>
+          <t>43949</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72325</t>
+          <t>75163</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>99463</t>
+          <t>101719</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>138764</t>
+          <t>141302</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50394</t>
+          <t>50123</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75316</t>
+          <t>76611</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>158289</t>
+          <t>158875</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>208609</t>
+          <t>206805</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>162661</t>
+          <t>164319</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>213998</t>
+          <t>214006</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92069</t>
+          <t>92245</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130418</t>
+          <t>131953</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>266679</t>
+          <t>266326</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>330670</t>
+          <t>327877</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>277405</t>
+          <t>277057</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>334990</t>
+          <t>335756</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>163304</t>
+          <t>166871</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>215204</t>
+          <t>215382</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>450915</t>
+          <t>455153</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>529870</t>
+          <t>536087</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>248853</t>
+          <t>251217</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>308847</t>
+          <t>307239</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>172295</t>
+          <t>172729</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>223356</t>
+          <t>221904</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>435728</t>
+          <t>435781</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>518738</t>
+          <t>512777</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>77473</t>
+          <t>75707</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>114323</t>
+          <t>114578</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49563</t>
+          <t>50612</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78771</t>
+          <t>80195</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>135907</t>
+          <t>137886</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>184083</t>
+          <t>185985</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>252491</t>
+          <t>250780</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>305254</t>
+          <t>306925</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>235267</t>
+          <t>235523</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>290751</t>
+          <t>292070</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>505201</t>
+          <t>502630</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>579730</t>
+          <t>578162</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>87693</t>
+          <t>87530</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>125835</t>
+          <t>126691</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>90696</t>
+          <t>90527</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>131437</t>
+          <t>130801</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>188433</t>
+          <t>186615</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>241344</t>
+          <t>238793</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>143523</t>
+          <t>143509</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>187250</t>
+          <t>186620</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>136575</t>
+          <t>135738</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>181123</t>
+          <t>181333</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>289679</t>
+          <t>292968</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>353292</t>
+          <t>355066</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>105253</t>
+          <t>105762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>147003</t>
+          <t>147673</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>108370</t>
+          <t>107023</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>151696</t>
+          <t>147802</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>224315</t>
+          <t>223877</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>288415</t>
+          <t>283683</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>27522</t>
+          <t>27655</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>51728</t>
+          <t>51477</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>43752</t>
+          <t>44817</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>74544</t>
+          <t>74303</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>78611</t>
+          <t>77955</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>115968</t>
+          <t>115288</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>165334</t>
+          <t>165930</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>210465</t>
+          <t>213505</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>258157</t>
+          <t>258158</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>313122</t>
+          <t>314635</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>435550</t>
+          <t>436580</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>507081</t>
+          <t>508449</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>32570</t>
+          <t>34002</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>57922</t>
+          <t>59797</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>91575</t>
+          <t>91882</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>134431</t>
+          <t>132952</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>132733</t>
+          <t>133359</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>181060</t>
+          <t>180171</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>62085</t>
+          <t>62257</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>92544</t>
+          <t>92906</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>209440</t>
+          <t>206891</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>262521</t>
+          <t>265411</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>285020</t>
+          <t>281423</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>346397</t>
+          <t>344693</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>53587</t>
+          <t>53878</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>84492</t>
+          <t>83933</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,47 +14399,47 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
+          <t>18,91%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>29,45%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>230863</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>202739</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>257483</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>21,41%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
           <t>18,8%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>29,65%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>230863</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>206337</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>260732</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>21,41%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>19,13%</t>
-        </is>
-      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>267664</t>
+          <t>267733</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>331187</t>
+          <t>331017</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>20637</t>
+          <t>20818</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>41616</t>
+          <t>43163</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>77530</t>
+          <t>78457</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>116296</t>
+          <t>118083</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>103816</t>
+          <t>104437</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>149256</t>
+          <t>148926</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>52974</t>
+          <t>51962</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>81400</t>
+          <t>80854</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>370838</t>
+          <t>373632</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>437697</t>
+          <t>440578</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>438859</t>
+          <t>437625</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>511953</t>
+          <t>515083</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>520529</t>
+          <t>521759</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>609466</t>
+          <t>612068</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>402140</t>
+          <t>400135</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>483399</t>
+          <t>481534</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>949765</t>
+          <t>951908</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1066428</t>
+          <t>1068965</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>860466</t>
+          <t>859995</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>963494</t>
+          <t>964940</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>772003</t>
+          <t>771220</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>871991</t>
+          <t>872804</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1659904</t>
+          <t>1663684</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1809320</t>
+          <t>1809089</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,7 +15038,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>739641</t>
+          <t>742149</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>840523</t>
+          <t>839852</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>724252</t>
+          <t>717715</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>819166</t>
+          <t>817024</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1487474</t>
+          <t>1486363</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1628112</t>
+          <t>1619962</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>226606</t>
+          <t>226876</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>291909</t>
+          <t>289510</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>266825</t>
+          <t>272187</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>335580</t>
+          <t>336444</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>514055</t>
+          <t>511516</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>605692</t>
+          <t>605154</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>795747</t>
+          <t>792053</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>895603</t>
+          <t>889963</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1130515</t>
+          <t>1132287</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1253697</t>
+          <t>1252501</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1952970</t>
+          <t>1960632</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2109290</t>
+          <t>2113728</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4503_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q4503_R-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69652</t>
+          <t>66875</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>101801</t>
+          <t>102396</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20850</t>
+          <t>21499</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42348</t>
+          <t>42533</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96179</t>
+          <t>98900</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135281</t>
+          <t>139799</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68964</t>
+          <t>68949</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103964</t>
+          <t>102782</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29504</t>
+          <t>30452</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>55942</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108383</t>
+          <t>108534</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150082</t>
+          <t>149712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121916</t>
+          <t>121731</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>161709</t>
+          <t>163475</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78374</t>
+          <t>78217</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>111172</t>
+          <t>111041</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>212469</t>
+          <t>211244</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>265290</t>
+          <t>264104</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,89%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44992</t>
+          <t>44116</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72651</t>
+          <t>73119</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35551</t>
+          <t>36582</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59717</t>
+          <t>60148</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85421</t>
+          <t>86427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125896</t>
+          <t>125013</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87623</t>
+          <t>84494</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121731</t>
+          <t>121502</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75616</t>
+          <t>77148</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107972</t>
+          <t>109101</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>173113</t>
+          <t>172001</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>219727</t>
+          <t>220253</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50262</t>
+          <t>49744</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80037</t>
+          <t>81509</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35188</t>
+          <t>33748</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62051</t>
+          <t>60150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93004</t>
+          <t>91051</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132815</t>
+          <t>130596</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44436</t>
+          <t>42639</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72851</t>
+          <t>71620</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31566</t>
+          <t>31617</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56896</t>
+          <t>56274</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83126</t>
+          <t>82440</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>119767</t>
+          <t>121827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81148</t>
+          <t>83082</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117607</t>
+          <t>117850</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>83262</t>
+          <t>83495</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118637</t>
+          <t>116356</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>176788</t>
+          <t>175266</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>225726</t>
+          <t>223808</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26239</t>
+          <t>26616</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51707</t>
+          <t>51334</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38748</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64371</t>
+          <t>64692</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71225</t>
+          <t>72978</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107442</t>
+          <t>108860</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92166</t>
+          <t>90913</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127166</t>
+          <t>126382</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111664</t>
+          <t>113587</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>149935</t>
+          <t>149749</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>212436</t>
+          <t>215451</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>265843</t>
+          <t>265657</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77523</t>
+          <t>79519</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>116124</t>
+          <t>115098</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12856</t>
+          <t>12997</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28515</t>
+          <t>30339</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99818</t>
+          <t>97742</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139205</t>
+          <t>138069</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89059</t>
+          <t>89714</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126526</t>
+          <t>126540</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14380</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32219</t>
+          <t>31833</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>106369</t>
+          <t>108929</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>149901</t>
+          <t>151802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>135718</t>
+          <t>135595</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178959</t>
+          <t>179291</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31393</t>
+          <t>32175</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55127</t>
+          <t>53860</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>176022</t>
+          <t>175348</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>225777</t>
+          <t>223315</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39505</t>
+          <t>39903</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66440</t>
+          <t>67780</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>11827</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28320</t>
+          <t>28176</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56774</t>
+          <t>57032</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88304</t>
+          <t>88979</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>109661</t>
+          <t>108469</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>150175</t>
+          <t>147143</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50618</t>
+          <t>51343</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75612</t>
+          <t>75902</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>167849</t>
+          <t>167891</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>214779</t>
+          <t>214030</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>250764</t>
+          <t>254121</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>309309</t>
+          <t>314437</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65420</t>
+          <t>65332</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98545</t>
+          <t>98749</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>330044</t>
+          <t>328267</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>398177</t>
+          <t>398590</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>221076</t>
+          <t>218207</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>274597</t>
+          <t>275327</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>70053</t>
+          <t>70252</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>105288</t>
+          <t>109079</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>302687</t>
+          <t>298397</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>369067</t>
+          <t>366320</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>310327</t>
+          <t>311393</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>373489</t>
+          <t>372659</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>156823</t>
+          <t>153786</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>202390</t>
+          <t>202082</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>485473</t>
+          <t>483113</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>560496</t>
+          <t>563954</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>87105</t>
+          <t>87464</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>123811</t>
+          <t>125946</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>74976</t>
+          <t>76857</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112522</t>
+          <t>113690</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>173114</t>
+          <t>172939</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>226652</t>
+          <t>226665</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>232599</t>
+          <t>231799</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>289845</t>
+          <t>289303</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>247824</t>
+          <t>248768</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>297170</t>
+          <t>300596</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>490705</t>
+          <t>495094</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>571583</t>
+          <t>576239</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,55%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>64897</t>
+          <t>64659</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>96048</t>
+          <t>96589</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54726</t>
+          <t>54202</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>86018</t>
+          <t>85642</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>127397</t>
+          <t>128453</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>173345</t>
+          <t>174506</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,98%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>52272</t>
+          <t>54098</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>83872</t>
+          <t>83721</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>48741</t>
+          <t>48388</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>78609</t>
+          <t>79790</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>111822</t>
+          <t>111308</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>154899</t>
+          <t>154339</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>90711</t>
+          <t>90466</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>127595</t>
+          <t>125941</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>117754</t>
+          <t>117020</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>158914</t>
+          <t>159416</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>217988</t>
+          <t>213671</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>273391</t>
+          <t>269395</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14922</t>
+          <t>15132</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>33766</t>
+          <t>33986</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>65814</t>
+          <t>65972</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>100615</t>
+          <t>100747</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>86991</t>
+          <t>86769</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>126074</t>
+          <t>126775</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>56056</t>
+          <t>56712</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>87030</t>
+          <t>87292</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>193417</t>
+          <t>191589</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>242101</t>
+          <t>239957</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>258430</t>
+          <t>258251</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>315453</t>
+          <t>315051</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16385</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>34612</t>
+          <t>35638</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>113599</t>
+          <t>111370</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>154233</t>
+          <t>156163</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>134188</t>
+          <t>135119</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>184692</t>
+          <t>181473</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>39716</t>
+          <t>40301</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>65151</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>93577</t>
+          <t>93902</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>136377</t>
+          <t>135472</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>142685</t>
+          <t>143442</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>190781</t>
+          <t>190092</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>96198</t>
+          <t>98025</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>130130</t>
+          <t>130902</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>259386</t>
+          <t>261306</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>321397</t>
+          <t>321315</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>370735</t>
+          <t>365488</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>438749</t>
+          <t>436688</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>25917</t>
+          <t>25133</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>46765</t>
+          <t>45822</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>114956</t>
+          <t>115387</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>158590</t>
+          <t>157567</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>148290</t>
+          <t>147574</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>195838</t>
+          <t>197101</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>59712</t>
+          <t>60096</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>90392</t>
+          <t>87506</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>539878</t>
+          <t>543622</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>610635</t>
+          <t>615343</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>609786</t>
+          <t>609351</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>690271</t>
+          <t>685425</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,36%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>590923</t>
+          <t>587789</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>679173</t>
+          <t>684294</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>342567</t>
+          <t>345647</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>417559</t>
+          <t>421472</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>951617</t>
+          <t>958424</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1071079</t>
+          <t>1074795</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>569751</t>
+          <t>573547</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>660895</t>
+          <t>658539</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>334555</t>
+          <t>336507</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>409442</t>
+          <t>406468</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>927946</t>
+          <t>925074</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1042129</t>
+          <t>1039509</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>912894</t>
+          <t>911675</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1018376</t>
+          <t>1017943</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>792018</t>
+          <t>788113</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>887007</t>
+          <t>887664</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1732581</t>
+          <t>1739130</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1878806</t>
+          <t>1876165</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>280760</t>
+          <t>277041</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>347230</t>
+          <t>344143</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>390013</t>
+          <t>387093</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>467670</t>
+          <t>468640</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>686131</t>
+          <t>691440</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>789593</t>
+          <t>793877</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>695117</t>
+          <t>696185</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>792436</t>
+          <t>791002</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1298907</t>
+          <t>1291950</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1412449</t>
+          <t>1407692</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2024073</t>
+          <t>2027142</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2174632</t>
+          <t>2171147</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80822</t>
+          <t>81641</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117380</t>
+          <t>117052</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35767</t>
+          <t>35184</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64590</t>
+          <t>65258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125255</t>
+          <t>123674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>172709</t>
+          <t>171526</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67611</t>
+          <t>67648</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102036</t>
+          <t>103121</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55327</t>
+          <t>55172</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87113</t>
+          <t>86565</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>131769</t>
+          <t>135301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177190</t>
+          <t>180022</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92883</t>
+          <t>95449</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134020</t>
+          <t>133956</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53705</t>
+          <t>53922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>84597</t>
+          <t>84314</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>158790</t>
+          <t>157434</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>209620</t>
+          <t>206010</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,58%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16447</t>
+          <t>16386</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38395</t>
+          <t>39441</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21879</t>
+          <t>22883</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45437</t>
+          <t>47597</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45609</t>
+          <t>44175</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78725</t>
+          <t>76030</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95043</t>
+          <t>96352</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>136285</t>
+          <t>134514</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73816</t>
+          <t>73679</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108819</t>
+          <t>108080</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177057</t>
+          <t>177665</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>231795</t>
+          <t>230005</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79797</t>
+          <t>81936</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116871</t>
+          <t>119651</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39616</t>
+          <t>38575</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69271</t>
+          <t>68720</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127864</t>
+          <t>126808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174066</t>
+          <t>173837</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65792</t>
+          <t>67928</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102626</t>
+          <t>103487</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36856</t>
+          <t>37985</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64331</t>
+          <t>65758</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112865</t>
+          <t>113611</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158586</t>
+          <t>158029</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76627</t>
+          <t>77525</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116033</t>
+          <t>115388</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62049</t>
+          <t>63660</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95470</t>
+          <t>95679</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>149617</t>
+          <t>148204</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>200757</t>
+          <t>198845</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15408</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34615</t>
+          <t>35709</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29879</t>
+          <t>30934</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57073</t>
+          <t>55985</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51890</t>
+          <t>51667</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84440</t>
+          <t>84543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97969</t>
+          <t>97158</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136823</t>
+          <t>136751</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95275</t>
+          <t>95997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134180</t>
+          <t>132939</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>203363</t>
+          <t>203831</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>256936</t>
+          <t>257957</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>154198</t>
+          <t>155772</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>200693</t>
+          <t>201740</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46377</t>
+          <t>46406</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72811</t>
+          <t>74430</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>209859</t>
+          <t>208133</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>263315</t>
+          <t>264643</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96550</t>
+          <t>96901</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135106</t>
+          <t>135368</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21642</t>
+          <t>22139</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43706</t>
+          <t>44696</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125331</t>
+          <t>126875</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>171362</t>
+          <t>169733</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>111910</t>
+          <t>110730</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>151945</t>
+          <t>153334</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39803</t>
+          <t>39933</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66754</t>
+          <t>65645</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>156921</t>
+          <t>160064</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>207677</t>
+          <t>208797</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16580</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36948</t>
+          <t>36899</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17041</t>
+          <t>16307</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36930</t>
+          <t>36575</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38232</t>
+          <t>36931</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67993</t>
+          <t>64667</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155561</t>
+          <t>156445</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>203831</t>
+          <t>203355</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76253</t>
+          <t>73813</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106367</t>
+          <t>107211</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>245816</t>
+          <t>241604</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>302029</t>
+          <t>300606</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>272304</t>
+          <t>272653</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>331053</t>
+          <t>332588</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>107707</t>
+          <t>109725</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>152396</t>
+          <t>151826</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>392011</t>
+          <t>393466</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>467219</t>
+          <t>471798</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>199875</t>
+          <t>200473</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>255674</t>
+          <t>256371</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>95623</t>
+          <t>95385</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>135696</t>
+          <t>136385</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>311627</t>
+          <t>310159</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>383464</t>
+          <t>377796</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>170943</t>
+          <t>170189</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>224225</t>
+          <t>223525</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>131564</t>
+          <t>131343</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>176644</t>
+          <t>176254</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>313427</t>
+          <t>311422</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>387649</t>
+          <t>382467</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42896</t>
+          <t>43389</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>75577</t>
+          <t>75681</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47598</t>
+          <t>48047</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77237</t>
+          <t>78993</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96086</t>
+          <t>97429</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>140658</t>
+          <t>143467</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>339930</t>
+          <t>342150</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>407457</t>
+          <t>404408</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>282630</t>
+          <t>278747</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>338391</t>
+          <t>334107</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>640518</t>
+          <t>637131</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>728378</t>
+          <t>723886</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>116356</t>
+          <t>117657</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>155829</t>
+          <t>156818</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>86924</t>
+          <t>88482</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>128880</t>
+          <t>128050</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>215947</t>
+          <t>217244</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>272344</t>
+          <t>273105</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>76576</t>
+          <t>77912</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>112088</t>
+          <t>112837</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>88829</t>
+          <t>89240</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>129050</t>
+          <t>130219</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>175582</t>
+          <t>176345</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>228300</t>
+          <t>230455</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>70603</t>
+          <t>70195</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>105685</t>
+          <t>104808</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>98300</t>
+          <t>100115</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>141234</t>
+          <t>140879</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>181557</t>
+          <t>182092</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>233705</t>
+          <t>234084</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>15106</t>
+          <t>14425</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>34569</t>
+          <t>33206</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>47125</t>
+          <t>48013</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>78824</t>
+          <t>79848</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>69730</t>
+          <t>68993</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>105079</t>
+          <t>105425</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>147929</t>
+          <t>146668</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>190737</t>
+          <t>190741</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>335024</t>
+          <t>333521</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>389191</t>
+          <t>391703</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>494945</t>
+          <t>496981</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>565248</t>
+          <t>566805</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>34016</t>
+          <t>33934</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>58913</t>
+          <t>60287</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>129518</t>
+          <t>129981</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>177629</t>
+          <t>176488</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>170072</t>
+          <t>171087</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>226259</t>
+          <t>225163</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>42606</t>
+          <t>41253</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>68499</t>
+          <t>67702</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>122160</t>
+          <t>121550</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>167977</t>
+          <t>166782</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>171543</t>
+          <t>173739</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>223008</t>
+          <t>227614</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>52456</t>
+          <t>52143</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>79449</t>
+          <t>80139</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>188202</t>
+          <t>187305</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>241589</t>
+          <t>240526</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>250660</t>
+          <t>254367</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>310297</t>
+          <t>313182</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16845</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>35311</t>
+          <t>36154</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>86168</t>
+          <t>87629</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>124051</t>
+          <t>124802</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>109423</t>
+          <t>110802</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>154942</t>
+          <t>152387</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>63864</t>
+          <t>63406</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>91691</t>
+          <t>93758</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>457808</t>
+          <t>459697</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>524303</t>
+          <t>527624</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>533851</t>
+          <t>530847</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>608461</t>
+          <t>603042</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>43,89%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>803300</t>
+          <t>803373</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>906830</t>
+          <t>911475</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>503727</t>
+          <t>506704</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>595009</t>
+          <t>589712</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1337384</t>
+          <t>1343106</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1472605</t>
+          <t>1480165</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>613004</t>
+          <t>612245</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>711074</t>
+          <t>708266</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>477006</t>
+          <t>480641</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>564796</t>
+          <t>568528</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1113924</t>
+          <t>1114101</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1247715</t>
+          <t>1250321</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>642359</t>
+          <t>636333</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>742731</t>
+          <t>733674</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>637458</t>
+          <t>632737</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>735255</t>
+          <t>733209</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1307941</t>
+          <t>1296384</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1444272</t>
+          <t>1442349</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>155295</t>
+          <t>153390</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>207837</t>
+          <t>207413</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>293148</t>
+          <t>295294</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>365856</t>
+          <t>367273</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>464230</t>
+          <t>465399</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>553073</t>
+          <t>549766</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>975001</t>
+          <t>974921</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1088509</t>
+          <t>1090850</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1395545</t>
+          <t>1389689</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1511930</t>
+          <t>1511517</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2399488</t>
+          <t>2402007</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2568157</t>
+          <t>2562885</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63410</t>
+          <t>63735</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>99043</t>
+          <t>96025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36836</t>
+          <t>35985</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63095</t>
+          <t>63016</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105702</t>
+          <t>106706</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>150840</t>
+          <t>152679</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>107646</t>
+          <t>107968</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146797</t>
+          <t>147537</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74712</t>
+          <t>74251</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109029</t>
+          <t>107137</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>191229</t>
+          <t>188323</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>240042</t>
+          <t>241244</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79646</t>
+          <t>80250</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117178</t>
+          <t>117656</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>76822</t>
+          <t>78383</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>108030</t>
+          <t>110017</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>165569</t>
+          <t>166515</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>213491</t>
+          <t>216272</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>19547</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44277</t>
+          <t>42766</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29896</t>
+          <t>31276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>56879</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57262</t>
+          <t>57297</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92183</t>
+          <t>91301</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77914</t>
+          <t>78509</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>113095</t>
+          <t>113873</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60661</t>
+          <t>59549</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90988</t>
+          <t>91972</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147011</t>
+          <t>147164</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>192310</t>
+          <t>193719</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44182</t>
+          <t>44439</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74351</t>
+          <t>74304</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29951</t>
+          <t>29315</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56394</t>
+          <t>55450</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80411</t>
+          <t>81039</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120958</t>
+          <t>121892</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90231</t>
+          <t>89035</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127413</t>
+          <t>127787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95249</t>
+          <t>94937</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131776</t>
+          <t>131861</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>194874</t>
+          <t>194843</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>245520</t>
+          <t>246073</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76154</t>
+          <t>75035</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>110072</t>
+          <t>110436</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>70951</t>
+          <t>73178</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>105964</t>
+          <t>105942</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>156750</t>
+          <t>157450</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>203447</t>
+          <t>205160</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13413</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30520</t>
+          <t>30624</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20240</t>
+          <t>20277</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41947</t>
+          <t>42687</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37621</t>
+          <t>38105</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64630</t>
+          <t>68598</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80682</t>
+          <t>79178</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113912</t>
+          <t>114126</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81142</t>
+          <t>80224</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>116511</t>
+          <t>116216</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171268</t>
+          <t>169581</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>221366</t>
+          <t>217912</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75559</t>
+          <t>75560</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>109292</t>
+          <t>109656</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14080</t>
+          <t>13891</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33755</t>
+          <t>33210</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>95912</t>
+          <t>95671</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136056</t>
+          <t>134287</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115992</t>
+          <t>116110</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154881</t>
+          <t>156094</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25062</t>
+          <t>24753</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46388</t>
+          <t>46375</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>147380</t>
+          <t>145558</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>193978</t>
+          <t>193514</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>111888</t>
+          <t>113204</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>150537</t>
+          <t>150722</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23260</t>
+          <t>23277</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43798</t>
+          <t>43540</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>141227</t>
+          <t>140196</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>186008</t>
+          <t>185916</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31006</t>
+          <t>31383</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56475</t>
+          <t>56821</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22698</t>
+          <t>23234</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43949</t>
+          <t>44279</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75163</t>
+          <t>73304</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>101719</t>
+          <t>102289</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>141302</t>
+          <t>141018</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50123</t>
+          <t>50836</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76611</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>158875</t>
+          <t>160103</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>206805</t>
+          <t>209114</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>164319</t>
+          <t>163741</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>214006</t>
+          <t>211630</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92245</t>
+          <t>92251</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131953</t>
+          <t>130662</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>266326</t>
+          <t>264319</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>327877</t>
+          <t>331188</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>277057</t>
+          <t>273633</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>335756</t>
+          <t>335094</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>166871</t>
+          <t>167097</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>215382</t>
+          <t>216564</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>455153</t>
+          <t>452181</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>536087</t>
+          <t>532479</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>251217</t>
+          <t>250373</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>307239</t>
+          <t>306173</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>172729</t>
+          <t>172767</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>221904</t>
+          <t>222812</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13075,7 +13075,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>435781</t>
+          <t>439489</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>512777</t>
+          <t>515084</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>75707</t>
+          <t>75519</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>114578</t>
+          <t>113870</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50612</t>
+          <t>50183</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>80195</t>
+          <t>81796</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>137886</t>
+          <t>134742</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>185985</t>
+          <t>183210</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>250780</t>
+          <t>253166</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>306925</t>
+          <t>311119</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>235523</t>
+          <t>235391</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>292070</t>
+          <t>290666</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>502630</t>
+          <t>499676</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>578162</t>
+          <t>583465</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>87530</t>
+          <t>87352</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>126691</t>
+          <t>123955</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>90527</t>
+          <t>91693</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>130801</t>
+          <t>129403</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>186615</t>
+          <t>185126</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>238793</t>
+          <t>239908</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>143509</t>
+          <t>143335</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>186620</t>
+          <t>184870</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>135738</t>
+          <t>136093</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>181333</t>
+          <t>181027</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>292968</t>
+          <t>293420</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>355066</t>
+          <t>355692</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>105762</t>
+          <t>105921</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>147673</t>
+          <t>144327</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>107023</t>
+          <t>108273</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>147802</t>
+          <t>149171</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>223877</t>
+          <t>226441</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>283683</t>
+          <t>281664</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>27655</t>
+          <t>27306</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>51477</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>44817</t>
+          <t>42784</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>74303</t>
+          <t>71558</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>77955</t>
+          <t>76715</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>115288</t>
+          <t>112716</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>165930</t>
+          <t>166881</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>213505</t>
+          <t>210929</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>258158</t>
+          <t>260139</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>314635</t>
+          <t>317151</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>436580</t>
+          <t>436451</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>508449</t>
+          <t>508413</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -14138,7 +14138,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>34002</t>
+          <t>32835</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>59797</t>
+          <t>58216</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>91882</t>
+          <t>91331</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>132952</t>
+          <t>134191</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>133359</t>
+          <t>132828</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>180171</t>
+          <t>178012</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>62257</t>
+          <t>61440</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>92906</t>
+          <t>91547</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>206891</t>
+          <t>209829</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>265411</t>
+          <t>266554</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>281423</t>
+          <t>282721</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>344693</t>
+          <t>346170</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>53878</t>
+          <t>54256</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>83933</t>
+          <t>82950</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>202739</t>
+          <t>204832</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>257483</t>
+          <t>259216</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>267733</t>
+          <t>269996</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>331017</t>
+          <t>331878</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>20818</t>
+          <t>20290</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>41779</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>78457</t>
+          <t>77826</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>118083</t>
+          <t>117304</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>104437</t>
+          <t>105694</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>148926</t>
+          <t>148690</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>51962</t>
+          <t>51583</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>80854</t>
+          <t>81269</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>373632</t>
+          <t>372328</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>440578</t>
+          <t>438539</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>437625</t>
+          <t>437536</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>515083</t>
+          <t>510553</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>521759</t>
+          <t>520202</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>612068</t>
+          <t>606366</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>400135</t>
+          <t>399434</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>481534</t>
+          <t>480324</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>951908</t>
+          <t>949986</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1068965</t>
+          <t>1065006</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>859995</t>
+          <t>863247</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>964940</t>
+          <t>963249</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>771220</t>
+          <t>771773</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>872804</t>
+          <t>868261</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1663684</t>
+          <t>1665730</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1809089</t>
+          <t>1812040</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>742149</t>
+          <t>741632</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>839852</t>
+          <t>843177</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>717715</t>
+          <t>715915</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>817024</t>
+          <t>819053</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1486363</t>
+          <t>1488610</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1619962</t>
+          <t>1633870</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>226876</t>
+          <t>227320</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>289510</t>
+          <t>290883</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>272187</t>
+          <t>273045</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>336444</t>
+          <t>339792</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>511516</t>
+          <t>515591</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>605154</t>
+          <t>608851</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>792053</t>
+          <t>791474</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>889963</t>
+          <t>894876</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1132287</t>
+          <t>1133432</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1252501</t>
+          <t>1250962</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1960632</t>
+          <t>1954901</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2113728</t>
+          <t>2110088</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
